--- a/NuevaData/Presentacion/Investigacion/FACTOR 2. ESTUDIANTES/a. Divulgación de propuestas académicas/F2_Divulgacion_y_Estudiantes_Investigacion.xlsx
+++ b/NuevaData/Presentacion/Investigacion/FACTOR 2. ESTUDIANTES/a. Divulgación de propuestas académicas/F2_Divulgacion_y_Estudiantes_Investigacion.xlsx
@@ -1673,7 +1673,7 @@
       </c>
       <c r="M12" s="13" t="inlineStr">
         <is>
-          <t>Además firmaron 9 docentes y representantes de grupos de investigación.</t>
+          <t>Además asistieron 9 docentes y representantes de grupos de investigación.</t>
         </is>
       </c>
     </row>

--- a/NuevaData/Presentacion/Investigacion/FACTOR 2. ESTUDIANTES/a. Divulgación de propuestas académicas/F2_Divulgacion_y_Estudiantes_Investigacion.xlsx
+++ b/NuevaData/Presentacion/Investigacion/FACTOR 2. ESTUDIANTES/a. Divulgación de propuestas académicas/F2_Divulgacion_y_Estudiantes_Investigacion.xlsx
@@ -10,13 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Páginas web" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura cohortes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Galería" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Galería" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Páginas web'!$A$4:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$M$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura cohortes'!$A$4:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -894,11 +892,6 @@
           <t>Registros de estudiantes de Investigación</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Cobertura inducción 2026-1</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
@@ -912,11 +905,6 @@
       <c r="E10" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>83 %</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="39" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -926,7 +914,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C10:D10"/>
@@ -935,14 +923,12 @@
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="G10:H10"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:H9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A6:B6"/>
   </mergeCells>
@@ -1964,142 +1950,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cobertura de las actividades sobre las cohortes nuevas de Investigación</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Admitidos: estudiantes con código de ingreso del periodo en el proyecto 595 según Cóndor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Cohorte</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Admitidos</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Actividad</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Asistentes de la cohorte</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Cobertura</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>2026-1</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Inducción 2026-1 (02/02/2026)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>83 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>2026-1</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Presentación de grupos de investigación (21/02/2026)</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>83 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>2026-3</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Socialización de grupos de investigación (22/08/2026)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>67 %</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:E7"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
